--- a/AlgoTrace_Report/ThongKe_TongHop.xlsx
+++ b/AlgoTrace_Report/ThongKe_TongHop.xlsx
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.474</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>300</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.211</v>
+        <v>0.207</v>
       </c>
       <c r="D3" t="n">
         <v>300</v>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="D4" t="n">
         <v>34</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.456</v>
+        <v>0.475</v>
       </c>
       <c r="D5" t="n">
         <v>300</v>
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>500</v>
@@ -600,16 +600,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D7" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>500</v>
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="D8" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>500</v>
@@ -681,16 +681,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.099</v>
+        <v>0.403</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
         <v>500</v>
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.155</v>
+        <v>0.191</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E11" t="n">
         <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>500</v>
@@ -735,16 +735,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
         <v>500</v>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.329</v>
+        <v>0.381</v>
       </c>
       <c r="D13" t="n">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E13" t="n">
         <v>34</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>500</v>
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.033</v>
+        <v>0.171</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="E14" t="n">
         <v>34</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>500</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
       <c r="D15" t="n">
         <v>165</v>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="D16" t="n">
         <v>34</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.149</v>
+        <v>0.175</v>
       </c>
       <c r="D17" t="n">
         <v>165</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.073</v>
+        <v>0.487</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
         <v>500</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.117</v>
+        <v>0.214</v>
       </c>
       <c r="D19" t="n">
         <v>300</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="D20" t="n">
         <v>34</v>
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.485</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E21" t="n">
         <v>34</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
         <v>500</v>

--- a/AlgoTrace_Report/ThongKe_TongHop.xlsx
+++ b/AlgoTrace_Report/ThongKe_TongHop.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Avg_TotalCost</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Avg_MemoryFringe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Success_Count</t>
         </is>
@@ -465,18 +470,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="D2" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="G2" t="n">
+        <v>108</v>
+      </c>
+      <c r="H2" t="n">
         <v>500</v>
       </c>
     </row>
@@ -492,18 +500,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.207</v>
+        <v>1.47</v>
       </c>
       <c r="D3" t="n">
-        <v>300</v>
+        <v>3008</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" t="n">
         <v>500</v>
       </c>
     </row>
@@ -519,18 +530,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.065</v>
+        <v>0.209</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="G4" t="n">
+        <v>109</v>
+      </c>
+      <c r="H4" t="n">
         <v>500</v>
       </c>
     </row>
@@ -546,18 +560,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.475</v>
+        <v>6.128</v>
       </c>
       <c r="D5" t="n">
-        <v>300</v>
+        <v>3008</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="n">
         <v>500</v>
       </c>
     </row>
@@ -573,18 +590,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.08</v>
+        <v>0.88</v>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>674</v>
       </c>
       <c r="E6" t="n">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>273</v>
       </c>
       <c r="G6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" t="n">
         <v>500</v>
       </c>
     </row>
@@ -600,18 +620,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.055</v>
+        <v>0.59</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>791</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
         <v>500</v>
       </c>
     </row>
@@ -627,18 +650,21 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.083</v>
+        <v>0.554</v>
       </c>
       <c r="D8" t="n">
-        <v>102</v>
+        <v>590</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="G8" t="n">
+        <v>105</v>
+      </c>
+      <c r="H8" t="n">
         <v>500</v>
       </c>
     </row>
@@ -654,18 +680,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>791</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>274</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
         <v>500</v>
       </c>
     </row>
@@ -681,18 +710,21 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.403</v>
+        <v>1.77</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>352</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="G10" t="n">
+        <v>110</v>
+      </c>
+      <c r="H10" t="n">
         <v>500</v>
       </c>
     </row>
@@ -708,18 +740,21 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.191</v>
+        <v>1.259</v>
       </c>
       <c r="D11" t="n">
-        <v>227</v>
+        <v>2417</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
         <v>500</v>
       </c>
     </row>
@@ -735,18 +770,21 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.128</v>
+        <v>0.666</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>549</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>486</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>485</v>
       </c>
       <c r="G12" t="n">
+        <v>377</v>
+      </c>
+      <c r="H12" t="n">
         <v>500</v>
       </c>
     </row>
@@ -762,18 +800,21 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.381</v>
+        <v>4.346</v>
       </c>
       <c r="D13" t="n">
-        <v>227</v>
+        <v>2417</v>
       </c>
       <c r="E13" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
         <v>500</v>
       </c>
     </row>
@@ -789,18 +830,21 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.171</v>
+        <v>0.227</v>
       </c>
       <c r="D14" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="E14" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="G14" t="n">
+        <v>32</v>
+      </c>
+      <c r="H14" t="n">
         <v>500</v>
       </c>
     </row>
@@ -816,18 +860,21 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.078</v>
+        <v>1.138</v>
       </c>
       <c r="D15" t="n">
-        <v>165</v>
+        <v>1658</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="G15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="n">
         <v>500</v>
       </c>
     </row>
@@ -843,18 +890,21 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.028</v>
+        <v>0.208</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
+        <v>32</v>
+      </c>
+      <c r="H16" t="n">
         <v>500</v>
       </c>
     </row>
@@ -870,18 +920,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.175</v>
+        <v>3.189</v>
       </c>
       <c r="D17" t="n">
-        <v>165</v>
+        <v>1658</v>
       </c>
       <c r="E17" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="n">
         <v>500</v>
       </c>
     </row>
@@ -897,18 +950,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.487</v>
+        <v>0.638</v>
       </c>
       <c r="D18" t="n">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="E18" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F18" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="G18" t="n">
+        <v>153</v>
+      </c>
+      <c r="H18" t="n">
         <v>500</v>
       </c>
     </row>
@@ -924,18 +980,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.214</v>
+        <v>1.555</v>
       </c>
       <c r="D19" t="n">
-        <v>300</v>
+        <v>3008</v>
       </c>
       <c r="E19" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
         <v>500</v>
       </c>
     </row>
@@ -951,18 +1010,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.035</v>
+        <v>0.176</v>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="E20" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="G20" t="n">
+        <v>109</v>
+      </c>
+      <c r="H20" t="n">
         <v>500</v>
       </c>
     </row>
@@ -978,18 +1040,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5669999999999999</v>
+        <v>6.759</v>
       </c>
       <c r="D21" t="n">
-        <v>293</v>
+        <v>2812</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="G21" t="n">
+        <v>59</v>
+      </c>
+      <c r="H21" t="n">
         <v>500</v>
       </c>
     </row>

--- a/AlgoTrace_Report/ThongKe_TongHop.xlsx
+++ b/AlgoTrace_Report/ThongKe_TongHop.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.475</v>
+        <v>0.576</v>
       </c>
       <c r="D2" t="n">
         <v>110</v>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.47</v>
+        <v>1.917</v>
       </c>
       <c r="D3" t="n">
         <v>3008</v>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.209</v>
+        <v>0.221</v>
       </c>
       <c r="D4" t="n">
         <v>110</v>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.128</v>
+        <v>7.24</v>
       </c>
       <c r="D5" t="n">
         <v>3008</v>
@@ -590,19 +590,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.88</v>
+        <v>1.619</v>
       </c>
       <c r="D6" t="n">
-        <v>674</v>
+        <v>931</v>
       </c>
       <c r="E6" t="n">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="F6" t="n">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
         <v>500</v>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.59</v>
+        <v>1.195</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>1113</v>
       </c>
       <c r="E7" t="n">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="F7" t="n">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
         <v>500</v>
@@ -650,19 +650,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.554</v>
+        <v>0.415</v>
       </c>
       <c r="D8" t="n">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="E8" t="n">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="F8" t="n">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="G8" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H8" t="n">
         <v>500</v>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.797</v>
+        <v>1.579</v>
       </c>
       <c r="D9" t="n">
-        <v>791</v>
+        <v>1113</v>
       </c>
       <c r="E9" t="n">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="F9" t="n">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
         <v>500</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.77</v>
+        <v>1.933</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>284</v>
       </c>
       <c r="E10" t="n">
         <v>110</v>
@@ -722,7 +722,7 @@
         <v>109</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="H10" t="n">
         <v>500</v>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.259</v>
+        <v>1.692</v>
       </c>
       <c r="D11" t="n">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="E11" t="n">
         <v>110</v>
@@ -752,7 +752,7 @@
         <v>109</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="n">
         <v>500</v>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.666</v>
+        <v>0.508</v>
       </c>
       <c r="D12" t="n">
-        <v>549</v>
+        <v>621</v>
       </c>
       <c r="E12" t="n">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="F12" t="n">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="G12" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="H12" t="n">
         <v>500</v>
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.346</v>
+        <v>5.622</v>
       </c>
       <c r="D13" t="n">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="E13" t="n">
         <v>110</v>
@@ -812,7 +812,7 @@
         <v>109</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H13" t="n">
         <v>500</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.227</v>
+        <v>0.236</v>
       </c>
       <c r="D14" t="n">
         <v>110</v>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.138</v>
+        <v>1.237</v>
       </c>
       <c r="D15" t="n">
         <v>1658</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
       <c r="D16" t="n">
         <v>110</v>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.189</v>
+        <v>3.366</v>
       </c>
       <c r="D17" t="n">
         <v>1658</v>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.638</v>
+        <v>0.756</v>
       </c>
       <c r="D18" t="n">
         <v>110</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.555</v>
+        <v>1.818</v>
       </c>
       <c r="D19" t="n">
         <v>3008</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.176</v>
+        <v>0.196</v>
       </c>
       <c r="D20" t="n">
         <v>110</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.759</v>
+        <v>7.853</v>
       </c>
       <c r="D21" t="n">
         <v>2812</v>
